--- a/backend/data/financials_by_company/0612.HK.xlsx
+++ b/backend/data/financials_by_company/0612.HK.xlsx
@@ -562,346 +562,346 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004209</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="E2" t="n">
-        <v>23858000</v>
+        <v>24981000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1987000</v>
+        <v>-18514000</v>
       </c>
       <c r="G2" t="n">
-        <v>3571000</v>
+        <v>19242000</v>
       </c>
       <c r="H2" t="n">
-        <v>1584000</v>
+        <v>728000</v>
       </c>
       <c r="I2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="J2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="K2" t="n">
-        <v>1563084000</v>
+        <v>1345568000</v>
       </c>
       <c r="L2" t="n">
-        <v>1561434000</v>
+        <v>1336003000</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3015</v>
+        <v>0.1227</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3015</v>
+        <v>0.1236</v>
       </c>
       <c r="O2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="P2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="R2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="S2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
       <c r="T2" t="n">
-        <v>-1990000</v>
+        <v>-73112000</v>
       </c>
       <c r="U2" t="n">
-        <v>-472800000</v>
+        <v>92018000</v>
       </c>
       <c r="V2" t="n">
-        <v>-2962000</v>
+        <v>-21859000</v>
       </c>
       <c r="W2" t="n">
-        <v>223828000</v>
+        <v>37667000</v>
       </c>
       <c r="X2" t="n">
-        <v>113223000</v>
+        <v>-67970000</v>
       </c>
       <c r="Y2" t="n">
-        <v>110605000</v>
+        <v>105637000</v>
       </c>
       <c r="Z2" t="n">
-        <v>110605000</v>
+        <v>105637000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-248972000</v>
+        <v>129685000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-248972000</v>
+        <v>129685000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="E3" t="n">
-        <v>25317000</v>
+        <v>26092000</v>
       </c>
       <c r="F3" t="n">
-        <v>-7336000</v>
+        <v>-16035000</v>
       </c>
       <c r="G3" t="n">
-        <v>8797000</v>
+        <v>16645000</v>
       </c>
       <c r="H3" t="n">
-        <v>1461000</v>
+        <v>610000</v>
       </c>
       <c r="I3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="J3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="K3" t="n">
-        <v>1524374000</v>
+        <v>1385450000</v>
       </c>
       <c r="L3" t="n">
-        <v>1520374000</v>
+        <v>1381450000</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2045</v>
+        <v>-0.2397</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2045</v>
+        <v>-0.2397</v>
       </c>
       <c r="O3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="P3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="R3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="S3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
       <c r="T3" t="n">
-        <v>8406000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-302526000</v>
+        <v>-331187000</v>
       </c>
       <c r="V3" t="n">
-        <v>5870000</v>
+        <v>-2798000</v>
       </c>
       <c r="W3" t="n">
-        <v>90240000</v>
+        <v>105579000</v>
       </c>
       <c r="X3" t="n">
-        <v>-28729000</v>
+        <v>190000</v>
       </c>
       <c r="Y3" t="n">
-        <v>118969000</v>
+        <v>105389000</v>
       </c>
       <c r="Z3" t="n">
-        <v>118969000</v>
+        <v>105389000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-212286000</v>
+        <v>-225608000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-212286000</v>
+        <v>-225608000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="E4" t="n">
-        <v>26092000</v>
+        <v>25317000</v>
       </c>
       <c r="F4" t="n">
-        <v>-16035000</v>
+        <v>-7336000</v>
       </c>
       <c r="G4" t="n">
-        <v>16645000</v>
+        <v>8797000</v>
       </c>
       <c r="H4" t="n">
-        <v>610000</v>
+        <v>1461000</v>
       </c>
       <c r="I4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="J4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="K4" t="n">
-        <v>1385450000</v>
+        <v>1524374000</v>
       </c>
       <c r="L4" t="n">
-        <v>1381450000</v>
+        <v>1520374000</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2397</v>
+        <v>-0.2045</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2397</v>
+        <v>-0.2045</v>
       </c>
       <c r="O4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="P4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="R4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="S4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>8406000</v>
       </c>
       <c r="U4" t="n">
-        <v>-331187000</v>
+        <v>-302526000</v>
       </c>
       <c r="V4" t="n">
-        <v>-2798000</v>
+        <v>5870000</v>
       </c>
       <c r="W4" t="n">
-        <v>105579000</v>
+        <v>90240000</v>
       </c>
       <c r="X4" t="n">
-        <v>190000</v>
+        <v>-28729000</v>
       </c>
       <c r="Y4" t="n">
-        <v>105389000</v>
+        <v>118969000</v>
       </c>
       <c r="Z4" t="n">
-        <v>105389000</v>
+        <v>118969000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-225608000</v>
+        <v>-212286000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-225608000</v>
+        <v>-212286000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.004209</v>
       </c>
       <c r="D5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="E5" t="n">
-        <v>24981000</v>
+        <v>23858000</v>
       </c>
       <c r="F5" t="n">
-        <v>-18514000</v>
+        <v>-1987000</v>
       </c>
       <c r="G5" t="n">
-        <v>19242000</v>
+        <v>3571000</v>
       </c>
       <c r="H5" t="n">
-        <v>728000</v>
+        <v>1584000</v>
       </c>
       <c r="I5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="J5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="K5" t="n">
-        <v>1345568000</v>
+        <v>1563084000</v>
       </c>
       <c r="L5" t="n">
-        <v>1336003000</v>
+        <v>1561434000</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1227</v>
+        <v>-0.3015</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1236</v>
+        <v>-0.3015</v>
       </c>
       <c r="O5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="P5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="Q5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="R5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="S5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
       <c r="T5" t="n">
-        <v>-73112000</v>
+        <v>-1990000</v>
       </c>
       <c r="U5" t="n">
-        <v>92018000</v>
+        <v>-472800000</v>
       </c>
       <c r="V5" t="n">
-        <v>-21859000</v>
+        <v>-2962000</v>
       </c>
       <c r="W5" t="n">
-        <v>37667000</v>
+        <v>223828000</v>
       </c>
       <c r="X5" t="n">
-        <v>-67970000</v>
+        <v>113223000</v>
       </c>
       <c r="Y5" t="n">
-        <v>105637000</v>
+        <v>110605000</v>
       </c>
       <c r="Z5" t="n">
-        <v>105637000</v>
+        <v>110605000</v>
       </c>
       <c r="AA5" t="n">
-        <v>129685000</v>
+        <v>-248972000</v>
       </c>
       <c r="AB5" t="n">
-        <v>129685000</v>
+        <v>-248972000</v>
       </c>
     </row>
   </sheetData>
@@ -1102,430 +1102,430 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1561433790</v>
+        <v>1350005000</v>
       </c>
       <c r="C2" t="n">
-        <v>1561433790</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>1350005000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>56210000</v>
+      </c>
       <c r="E2" t="n">
-        <v>10209000</v>
+        <v>178687000</v>
       </c>
       <c r="F2" t="n">
-        <v>498978000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>1261107000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1440353000</v>
+      </c>
       <c r="H2" t="n">
-        <v>498978000</v>
+        <v>1261107000</v>
       </c>
       <c r="I2" t="n">
-        <v>501134000</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1272262000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1440353000</v>
+      </c>
       <c r="K2" t="n">
-        <v>501134000</v>
+        <v>1272262000</v>
       </c>
       <c r="L2" t="n">
-        <v>501134000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3821000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1294972000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1249655000</v>
-      </c>
+        <v>1272262000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>78072000</v>
+        <v>67500000</v>
       </c>
       <c r="Q2" t="n">
-        <v>78072000</v>
+        <v>67500000</v>
       </c>
       <c r="R2" t="n">
-        <v>15961000</v>
+        <v>187077000</v>
       </c>
       <c r="S2" t="n">
-        <v>10209000</v>
+        <v>178687000</v>
       </c>
       <c r="T2" t="n">
-        <v>3944000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
+        <v>6805000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>3944000</v>
+        <v>6805000</v>
       </c>
       <c r="W2" t="n">
-        <v>517095000</v>
+        <v>1459339000</v>
       </c>
       <c r="X2" t="n">
-        <v>114040000</v>
+        <v>773179000</v>
       </c>
       <c r="Y2" t="n">
-        <v>114040000</v>
+        <v>773179000</v>
       </c>
       <c r="Z2" t="n">
-        <v>76431000</v>
+        <v>99094000</v>
       </c>
       <c r="AA2" t="n">
-        <v>37609000</v>
+        <v>674085000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2156000</v>
+        <v>11155000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2156000</v>
+        <v>11155000</v>
       </c>
       <c r="AD2" t="n">
-        <v>312560000</v>
+        <v>530111000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-185576000</v>
+        <v>-37065000</v>
       </c>
       <c r="AF2" t="n">
-        <v>498136000</v>
+        <v>567176000</v>
       </c>
       <c r="AG2" t="n">
-        <v>18360000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>19717000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>16325000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>66253000</v>
+        <v>111881000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>66253000</v>
+        <v>111881000</v>
       </c>
       <c r="AK2" t="n">
-        <v>66253000</v>
+        <v>111881000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1561433790</v>
+        <v>1420290000</v>
       </c>
       <c r="C3" t="n">
-        <v>1561433790</v>
+        <v>1420290000</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>67853000</v>
+        <v>111318000</v>
       </c>
       <c r="F3" t="n">
-        <v>984250000</v>
+        <v>1086886000</v>
       </c>
       <c r="G3" t="n">
-        <v>1034139000</v>
+        <v>1190664000</v>
       </c>
       <c r="H3" t="n">
-        <v>984250000</v>
+        <v>1086886000</v>
       </c>
       <c r="I3" t="n">
-        <v>989245000</v>
+        <v>1096692000</v>
       </c>
       <c r="J3" t="n">
-        <v>1034139000</v>
+        <v>1190664000</v>
       </c>
       <c r="K3" t="n">
-        <v>989245000</v>
+        <v>1096692000</v>
       </c>
       <c r="L3" t="n">
-        <v>989245000</v>
+        <v>1096692000</v>
       </c>
       <c r="M3" t="n">
-        <v>4880000</v>
+        <v>2104000</v>
       </c>
       <c r="N3" t="n">
-        <v>-823787000</v>
+        <v>-503489000</v>
       </c>
       <c r="O3" t="n">
-        <v>1249655000</v>
+        <v>1031217000</v>
       </c>
       <c r="P3" t="n">
-        <v>78072000</v>
+        <v>71014000</v>
       </c>
       <c r="Q3" t="n">
-        <v>78072000</v>
+        <v>71014000</v>
       </c>
       <c r="R3" t="n">
-        <v>78616000</v>
+        <v>120770000</v>
       </c>
       <c r="S3" t="n">
-        <v>67853000</v>
+        <v>111318000</v>
       </c>
       <c r="T3" t="n">
-        <v>4269000</v>
+        <v>5057000</v>
       </c>
       <c r="U3" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4261000</v>
+        <v>5057000</v>
       </c>
       <c r="W3" t="n">
-        <v>1067861000</v>
+        <v>1217462000</v>
       </c>
       <c r="X3" t="n">
-        <v>402780000</v>
+        <v>604588000</v>
       </c>
       <c r="Y3" t="n">
-        <v>402780000</v>
+        <v>604588000</v>
       </c>
       <c r="Z3" t="n">
-        <v>133603000</v>
+        <v>107309000</v>
       </c>
       <c r="AA3" t="n">
-        <v>269177000</v>
+        <v>497279000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4995000</v>
+        <v>9806000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4995000</v>
+        <v>9806000</v>
       </c>
       <c r="AD3" t="n">
-        <v>467429000</v>
+        <v>484033000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-58203000</v>
+        <v>-46907000</v>
       </c>
       <c r="AF3" t="n">
-        <v>525632000</v>
+        <v>530940000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13934000</v>
+        <v>7529000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>173342000</v>
+        <v>101029000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173342000</v>
+        <v>101029000</v>
       </c>
       <c r="AK3" t="n">
-        <v>173342000</v>
+        <v>101029000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1420290000</v>
+        <v>1561433790</v>
       </c>
       <c r="C4" t="n">
-        <v>1420290000</v>
+        <v>1561433790</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>111318000</v>
+        <v>67853000</v>
       </c>
       <c r="F4" t="n">
-        <v>1086886000</v>
+        <v>984250000</v>
       </c>
       <c r="G4" t="n">
-        <v>1190664000</v>
+        <v>1034139000</v>
       </c>
       <c r="H4" t="n">
-        <v>1086886000</v>
+        <v>984250000</v>
       </c>
       <c r="I4" t="n">
-        <v>1096692000</v>
+        <v>989245000</v>
       </c>
       <c r="J4" t="n">
-        <v>1190664000</v>
+        <v>1034139000</v>
       </c>
       <c r="K4" t="n">
-        <v>1096692000</v>
+        <v>989245000</v>
       </c>
       <c r="L4" t="n">
-        <v>1096692000</v>
+        <v>989245000</v>
       </c>
       <c r="M4" t="n">
-        <v>2104000</v>
+        <v>4880000</v>
       </c>
       <c r="N4" t="n">
-        <v>-503489000</v>
+        <v>-823787000</v>
       </c>
       <c r="O4" t="n">
-        <v>1031217000</v>
+        <v>1249655000</v>
       </c>
       <c r="P4" t="n">
-        <v>71014000</v>
+        <v>78072000</v>
       </c>
       <c r="Q4" t="n">
-        <v>71014000</v>
+        <v>78072000</v>
       </c>
       <c r="R4" t="n">
-        <v>120770000</v>
+        <v>78616000</v>
       </c>
       <c r="S4" t="n">
-        <v>111318000</v>
+        <v>67853000</v>
       </c>
       <c r="T4" t="n">
-        <v>5057000</v>
+        <v>4269000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="V4" t="n">
-        <v>5057000</v>
+        <v>4261000</v>
       </c>
       <c r="W4" t="n">
-        <v>1217462000</v>
+        <v>1067861000</v>
       </c>
       <c r="X4" t="n">
-        <v>604588000</v>
+        <v>402780000</v>
       </c>
       <c r="Y4" t="n">
-        <v>604588000</v>
+        <v>402780000</v>
       </c>
       <c r="Z4" t="n">
-        <v>107309000</v>
+        <v>133603000</v>
       </c>
       <c r="AA4" t="n">
-        <v>497279000</v>
+        <v>269177000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9806000</v>
+        <v>4995000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9806000</v>
+        <v>4995000</v>
       </c>
       <c r="AD4" t="n">
-        <v>484033000</v>
+        <v>467429000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-46907000</v>
+        <v>-58203000</v>
       </c>
       <c r="AF4" t="n">
-        <v>530940000</v>
+        <v>525632000</v>
       </c>
       <c r="AG4" t="n">
-        <v>7529000</v>
+        <v>13934000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>101029000</v>
+        <v>173342000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>101029000</v>
+        <v>173342000</v>
       </c>
       <c r="AK4" t="n">
-        <v>101029000</v>
+        <v>173342000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1350005000</v>
+        <v>1561433790</v>
       </c>
       <c r="C5" t="n">
-        <v>1350005000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>56210000</v>
-      </c>
+        <v>1561433790</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>178687000</v>
+        <v>10209000</v>
       </c>
       <c r="F5" t="n">
-        <v>1261107000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1440353000</v>
-      </c>
+        <v>498978000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1261107000</v>
+        <v>498978000</v>
       </c>
       <c r="I5" t="n">
-        <v>1272262000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1440353000</v>
-      </c>
+        <v>501134000</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>1272262000</v>
+        <v>501134000</v>
       </c>
       <c r="L5" t="n">
-        <v>1272262000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>501134000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3821000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1294972000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1249655000</v>
+      </c>
       <c r="P5" t="n">
-        <v>67500000</v>
+        <v>78072000</v>
       </c>
       <c r="Q5" t="n">
-        <v>67500000</v>
+        <v>78072000</v>
       </c>
       <c r="R5" t="n">
-        <v>187077000</v>
+        <v>15961000</v>
       </c>
       <c r="S5" t="n">
-        <v>178687000</v>
+        <v>10209000</v>
       </c>
       <c r="T5" t="n">
-        <v>6805000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>3944000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
       <c r="V5" t="n">
-        <v>6805000</v>
+        <v>3944000</v>
       </c>
       <c r="W5" t="n">
-        <v>1459339000</v>
+        <v>517095000</v>
       </c>
       <c r="X5" t="n">
-        <v>773179000</v>
+        <v>114040000</v>
       </c>
       <c r="Y5" t="n">
-        <v>773179000</v>
+        <v>114040000</v>
       </c>
       <c r="Z5" t="n">
-        <v>99094000</v>
+        <v>76431000</v>
       </c>
       <c r="AA5" t="n">
-        <v>674085000</v>
+        <v>37609000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11155000</v>
+        <v>2156000</v>
       </c>
       <c r="AC5" t="n">
-        <v>11155000</v>
+        <v>2156000</v>
       </c>
       <c r="AD5" t="n">
-        <v>530111000</v>
+        <v>312560000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-37065000</v>
+        <v>-185576000</v>
       </c>
       <c r="AF5" t="n">
-        <v>567176000</v>
+        <v>498136000</v>
       </c>
       <c r="AG5" t="n">
-        <v>19717000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16325000</v>
-      </c>
+        <v>18360000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>111881000</v>
+        <v>66253000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>111881000</v>
+        <v>66253000</v>
       </c>
       <c r="AK5" t="n">
-        <v>111881000</v>
+        <v>66253000</v>
       </c>
     </row>
   </sheetData>
@@ -1756,43 +1756,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-51393000</v>
+        <v>-14762000</v>
       </c>
       <c r="C2" t="n">
-        <v>-59923000</v>
+        <v>-103767000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>35220000</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>17813000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1050000</v>
+        <v>-215000</v>
       </c>
       <c r="G2" t="n">
-        <v>66253000</v>
+        <v>111881000</v>
       </c>
       <c r="H2" t="n">
-        <v>173342000</v>
+        <v>164127000</v>
       </c>
       <c r="I2" t="n">
-        <v>-656000</v>
+        <v>1162000</v>
       </c>
       <c r="J2" t="n">
-        <v>-106433000</v>
+        <v>-53408000</v>
       </c>
       <c r="K2" t="n">
-        <v>-61375000</v>
+        <v>-65481000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1452000</v>
+        <v>-14747000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1801,127 +1801,121 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>17813000</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>17813000</v>
       </c>
       <c r="R2" t="n">
-        <v>-59923000</v>
+        <v>-68547000</v>
       </c>
       <c r="S2" t="n">
-        <v>-59923000</v>
+        <v>-68547000</v>
       </c>
       <c r="T2" t="n">
-        <v>-59923000</v>
+        <v>-103767000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>35220000</v>
       </c>
       <c r="V2" t="n">
-        <v>5285000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
+        <v>26620000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>6235000</v>
+        <v>26835000</v>
       </c>
       <c r="Z2" t="n">
-        <v>6235000</v>
+        <v>26835000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-950000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>100000</v>
-      </c>
+        <v>-215000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-1050000</v>
+        <v>-215000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-50343000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-8000</v>
-      </c>
+        <v>-14547000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>1277000</v>
+        <v>480000</v>
       </c>
       <c r="AG2" t="n">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3035000</v>
+        <v>2591000</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>18145000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-17000</v>
+        <v>-706000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3018000</v>
+        <v>-14848000</v>
       </c>
       <c r="AM2" t="n">
-        <v>112706000</v>
+        <v>-119564000</v>
       </c>
       <c r="AN2" t="n">
-        <v>23858000</v>
+        <v>24981000</v>
       </c>
       <c r="AO2" t="n">
-        <v>23858000</v>
+        <v>24981000</v>
       </c>
       <c r="AP2" t="n">
-        <v>285552000</v>
+        <v>-88165000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-470810000</v>
+        <v>165130000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-82246000</v>
+        <v>-110188000</v>
       </c>
       <c r="C3" t="n">
-        <v>-77417000</v>
+        <v>-144986000</v>
       </c>
       <c r="D3" t="n">
-        <v>12000000</v>
+        <v>52340000</v>
       </c>
       <c r="E3" t="n">
-        <v>225267000</v>
+        <v>207557000</v>
       </c>
       <c r="F3" t="n">
-        <v>-2771000</v>
+        <v>-1054000</v>
       </c>
       <c r="G3" t="n">
-        <v>173342000</v>
+        <v>101029000</v>
       </c>
       <c r="H3" t="n">
-        <v>101029000</v>
+        <v>111881000</v>
       </c>
       <c r="I3" t="n">
-        <v>-873000</v>
+        <v>-3505000</v>
       </c>
       <c r="J3" t="n">
-        <v>73186000</v>
+        <v>-7347000</v>
       </c>
       <c r="K3" t="n">
-        <v>154381000</v>
+        <v>102791000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-5469000</v>
+        <v>-12120000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1930,127 +1924,127 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>225267000</v>
+        <v>207557000</v>
       </c>
       <c r="Q3" t="n">
-        <v>225267000</v>
+        <v>207557000</v>
       </c>
       <c r="R3" t="n">
-        <v>-65417000</v>
+        <v>-92646000</v>
       </c>
       <c r="S3" t="n">
-        <v>-65417000</v>
+        <v>-92646000</v>
       </c>
       <c r="T3" t="n">
-        <v>-77417000</v>
+        <v>-144986000</v>
       </c>
       <c r="U3" t="n">
-        <v>12000000</v>
+        <v>52340000</v>
       </c>
       <c r="V3" t="n">
-        <v>-1720000</v>
+        <v>-1004000</v>
       </c>
       <c r="W3" t="n">
-        <v>-21891000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-21891000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>22911000</v>
+        <v>50000</v>
       </c>
       <c r="Z3" t="n">
-        <v>22911000</v>
+        <v>50000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2740000</v>
+        <v>-1054000</v>
       </c>
       <c r="AB3" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2771000</v>
+        <v>-1054000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-79475000</v>
+        <v>-109134000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1045000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
+        <v>252000</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-7918000</v>
+        <v>17800000</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>194000</v>
+        <v>2810000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-8112000</v>
+        <v>14990000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-8147000</v>
+        <v>17345000</v>
       </c>
       <c r="AN3" t="n">
-        <v>25317000</v>
+        <v>26092000</v>
       </c>
       <c r="AO3" t="n">
-        <v>25317000</v>
+        <v>26092000</v>
       </c>
       <c r="AP3" t="n">
-        <v>221168000</v>
+        <v>160564000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-310932000</v>
+        <v>-331187000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-110188000</v>
+        <v>-82246000</v>
       </c>
       <c r="C4" t="n">
-        <v>-144986000</v>
+        <v>-77417000</v>
       </c>
       <c r="D4" t="n">
-        <v>52340000</v>
+        <v>12000000</v>
       </c>
       <c r="E4" t="n">
-        <v>207557000</v>
+        <v>225267000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1054000</v>
+        <v>-2771000</v>
       </c>
       <c r="G4" t="n">
+        <v>173342000</v>
+      </c>
+      <c r="H4" t="n">
         <v>101029000</v>
       </c>
-      <c r="H4" t="n">
-        <v>111881000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-3505000</v>
+        <v>-873000</v>
       </c>
       <c r="J4" t="n">
-        <v>-7347000</v>
+        <v>73186000</v>
       </c>
       <c r="K4" t="n">
-        <v>102791000</v>
+        <v>154381000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-12120000</v>
+        <v>-5469000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -2059,127 +2053,127 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>207557000</v>
+        <v>225267000</v>
       </c>
       <c r="Q4" t="n">
-        <v>207557000</v>
+        <v>225267000</v>
       </c>
       <c r="R4" t="n">
-        <v>-92646000</v>
+        <v>-65417000</v>
       </c>
       <c r="S4" t="n">
-        <v>-92646000</v>
+        <v>-65417000</v>
       </c>
       <c r="T4" t="n">
-        <v>-144986000</v>
+        <v>-77417000</v>
       </c>
       <c r="U4" t="n">
-        <v>52340000</v>
+        <v>12000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-1004000</v>
+        <v>-1720000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-21891000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-21891000</v>
       </c>
       <c r="Y4" t="n">
-        <v>50000</v>
+        <v>22911000</v>
       </c>
       <c r="Z4" t="n">
-        <v>50000</v>
+        <v>22911000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1054000</v>
+        <v>-2740000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1054000</v>
+        <v>-2771000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-109134000</v>
+        <v>-79475000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="AF4" t="n">
-        <v>252000</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>1045000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4" t="n">
-        <v>17800000</v>
+        <v>-7918000</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>2810000</v>
+        <v>194000</v>
       </c>
       <c r="AL4" t="n">
-        <v>14990000</v>
+        <v>-8112000</v>
       </c>
       <c r="AM4" t="n">
-        <v>17345000</v>
+        <v>-8147000</v>
       </c>
       <c r="AN4" t="n">
-        <v>26092000</v>
+        <v>25317000</v>
       </c>
       <c r="AO4" t="n">
-        <v>26092000</v>
+        <v>25317000</v>
       </c>
       <c r="AP4" t="n">
-        <v>160564000</v>
+        <v>221168000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-331187000</v>
+        <v>-310932000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-14762000</v>
+        <v>-51393000</v>
       </c>
       <c r="C5" t="n">
-        <v>-103767000</v>
+        <v>-59923000</v>
       </c>
       <c r="D5" t="n">
-        <v>35220000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>17813000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-215000</v>
+        <v>-1050000</v>
       </c>
       <c r="G5" t="n">
-        <v>111881000</v>
+        <v>66253000</v>
       </c>
       <c r="H5" t="n">
-        <v>164127000</v>
+        <v>173342000</v>
       </c>
       <c r="I5" t="n">
-        <v>1162000</v>
+        <v>-656000</v>
       </c>
       <c r="J5" t="n">
-        <v>-53408000</v>
+        <v>-106433000</v>
       </c>
       <c r="K5" t="n">
-        <v>-65481000</v>
+        <v>-61375000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-14747000</v>
+        <v>-1452000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -2188,80 +2182,86 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>17813000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>17813000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-68547000</v>
+        <v>-59923000</v>
       </c>
       <c r="S5" t="n">
-        <v>-68547000</v>
+        <v>-59923000</v>
       </c>
       <c r="T5" t="n">
-        <v>-103767000</v>
+        <v>-59923000</v>
       </c>
       <c r="U5" t="n">
-        <v>35220000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>26620000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+        <v>5285000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" t="n">
-        <v>26835000</v>
+        <v>6235000</v>
       </c>
       <c r="Z5" t="n">
-        <v>26835000</v>
+        <v>6235000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-215000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-950000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>100000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-215000</v>
+        <v>-1050000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-14547000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>-50343000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-8000</v>
+      </c>
       <c r="AF5" t="n">
-        <v>480000</v>
+        <v>1277000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2591000</v>
+        <v>-3035000</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>18145000</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>-706000</v>
+        <v>-17000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-14848000</v>
+        <v>-3018000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-119564000</v>
+        <v>112706000</v>
       </c>
       <c r="AN5" t="n">
-        <v>24981000</v>
+        <v>23858000</v>
       </c>
       <c r="AO5" t="n">
-        <v>24981000</v>
+        <v>23858000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-88165000</v>
+        <v>285552000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>165130000</v>
+        <v>-470810000</v>
       </c>
     </row>
   </sheetData>
@@ -2786,197 +2786,197 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.283</v>
+        <v>1.296</v>
       </c>
       <c r="AE2" t="n">
         <v>8152000</v>
@@ -3145,7 +3145,7 @@
         <v>0.188</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9</v>
+        <v>0.48</v>
       </c>
       <c r="AR2" t="n">
         <v>28.35</v>
@@ -3233,10 +3233,10 @@
         <v>-8.175000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.5649351</v>
+        <v>-0.18292683</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.02</v>
@@ -3344,149 +3344,149 @@
         </is>
       </c>
       <c r="CX2" t="n">
+        <v>-30.927834</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>China Ding Yi Feng Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>DING YI FENG</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>1751011731</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>finmb_20388607</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Carmen Century Investment Limited</t>
+        </is>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1134696600000</v>
+      </c>
+      <c r="DW2" t="n">
         <v>-0.15</v>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>0.25 - 0.34</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
         <v>0.14700001</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="EB2" t="n">
         <v>0.781915</v>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>0.188 - 0.9</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.56499994</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.62777776</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-56.493507</v>
-      </c>
-      <c r="DH2" t="n">
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>0.188 - 0.48</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.14499998</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.3020833</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-18.292683</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1742392834</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="EH2" t="n">
         <v>1742392834</v>
       </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>-0.07000000000000001</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>China Ding Yi Feng Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1134696600000</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>DING YI FENG</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Carmen Century Investment Limited</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1751011731</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>finmb_20388607</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>-30.927834</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.335</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
